--- a/Testing/Enterprise-Selenium/Test Results/Excel/Summary_Report.xlsx
+++ b/Testing/Enterprise-Selenium/Test Results/Excel/Summary_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Passed Tests</v>
       </c>
       <c r="B4">
-        <v>452</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5">
@@ -436,7 +436,7 @@
         <v>Failed Tests</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,7 @@
         <v>Skipped Tests</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -452,7 +452,7 @@
         <v>Pass Rate (%)</v>
       </c>
       <c r="B7" t="str">
-        <v>96.17%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="8">
